--- a/T2 - Práctica React - 29012026/T2 - Tabla puntuación.xlsx
+++ b/T2 - Práctica React - 29012026/T2 - Tabla puntuación.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\IES\02DAMDESINT-25-26\Práctica UD3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Equipo\Desktop\Oficina-DAM\2ºDAM\DIDAHE\T2 - Práctica React - 29012026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0935229-C322-44A9-8945-69D4176CBD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27821D60-77EF-4917-8C44-5A13068CD354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{360ED738-5174-48CE-9540-6C3D0194F059}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="28800" windowHeight="15780" xr2:uid="{360ED738-5174-48CE-9540-6C3D0194F059}"/>
   </bookViews>
   <sheets>
     <sheet name="PUNTUACIÓN" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -89,12 +87,6 @@
     <t>LISTADO CON DATAGRID</t>
   </si>
   <si>
-    <t>NOMBRE ENTIDAD 1</t>
-  </si>
-  <si>
-    <t>NOMBRE ENTIDAD 2</t>
-  </si>
-  <si>
     <t>TABLA DE PUNTUACIÓN DE LA PRÁCTICA</t>
   </si>
   <si>
@@ -135,6 +127,12 @@
   </si>
   <si>
     <t>MAQUETACIÓN RESPONSIVE GRID</t>
+  </si>
+  <si>
+    <t>CURSO</t>
+  </si>
+  <si>
+    <t>PLATAFORMA</t>
   </si>
 </sst>
 </file>
@@ -414,6 +412,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -426,28 +446,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -783,94 +781,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160D82D4-F57D-4CFD-BFA4-F37D7E897A75}">
   <dimension ref="C1:H30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="31.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C2" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
       <c r="G2" s="16"/>
-      <c r="H2" s="34"/>
-    </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H2" s="24"/>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
       <c r="G3" s="18"/>
-      <c r="H3" s="34"/>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
+        <v>20</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
       <c r="G4" s="18"/>
-      <c r="H4" s="34"/>
-    </row>
-    <row r="5" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
       <c r="G5" s="21"/>
-      <c r="H5" s="34"/>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="28"/>
+      <c r="D9" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="26"/>
       <c r="F9" s="3">
         <v>0.5</v>
       </c>
@@ -879,14 +877,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="28"/>
+      <c r="D10" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="26"/>
       <c r="F10" s="3">
         <v>0.5</v>
       </c>
@@ -895,14 +893,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="28"/>
+      <c r="D11" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="26"/>
       <c r="F11" s="3">
         <v>0.5</v>
       </c>
@@ -911,14 +909,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="28"/>
+        <v>25</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="26"/>
       <c r="F12" s="3">
         <v>0.5</v>
       </c>
@@ -927,38 +925,38 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" s="22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="4"/>
       <c r="F13" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13" s="12">
         <f>MIN(2,SUM(G9:G12))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:8" ht="27" x14ac:dyDescent="0.25">
       <c r="C14" s="1"/>
       <c r="D14" s="10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C15" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>2</v>
@@ -967,14 +965,14 @@
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G15" s="13">
         <f>COUNTIF(D15:E15,"=X")*0.75</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="7" t="s">
         <v>6</v>
       </c>
@@ -992,7 +990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C17" s="7" t="s">
         <v>7</v>
       </c>
@@ -1010,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C18" s="7" t="s">
         <v>8</v>
       </c>
@@ -1028,7 +1026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C19" s="7" t="s">
         <v>9</v>
       </c>
@@ -1039,43 +1037,43 @@
         <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G19" s="13">
         <f>COUNTIF(D19:E19,"=X")*0.75</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C20" s="22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G20" s="12">
         <f>MIN(6,SUM(G15:G19))</f>
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:7" ht="27" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
       <c r="D21" s="10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>5</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
@@ -1091,7 +1089,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C23" s="7" t="s">
         <v>13</v>
       </c>
@@ -1107,7 +1105,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C24" s="7" t="s">
         <v>15</v>
       </c>
@@ -1123,7 +1121,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C25" s="7" t="s">
         <v>16</v>
       </c>
@@ -1139,14 +1137,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="32"/>
+      <c r="D26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="30"/>
       <c r="F26" s="3">
         <v>0.5</v>
       </c>
@@ -1155,14 +1153,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="32"/>
+        <v>30</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="30"/>
       <c r="F27" s="3">
         <v>0.5</v>
       </c>
@@ -1171,14 +1169,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C28" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="28"/>
+      <c r="D28" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="26"/>
       <c r="F28" s="3">
         <v>0.5</v>
       </c>
@@ -1187,27 +1185,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C29" s="22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G29" s="12">
         <f>MIN(2,SUM(G23:G28))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C30" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
+    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C30" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29"/>
       <c r="G30" s="8">
         <f>MIN(10,SUM(G29,G20,G13))</f>
         <v>10</v>
@@ -1215,16 +1213,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/T2 - Práctica React - 29012026/T2 - Tabla puntuación.xlsx
+++ b/T2 - Práctica React - 29012026/T2 - Tabla puntuación.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Equipo\Desktop\Oficina-DAM\2ºDAM\DIDAHE\T2 - Práctica React - 29012026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27821D60-77EF-4917-8C44-5A13068CD354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3646E4-7083-4ADC-B52B-44451E6760A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="28800" windowHeight="15780" xr2:uid="{360ED738-5174-48CE-9540-6C3D0194F059}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{360ED738-5174-48CE-9540-6C3D0194F059}"/>
   </bookViews>
   <sheets>
     <sheet name="PUNTUACIÓN" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
   <si>
     <t>APLICACIÓN</t>
   </si>
@@ -416,6 +416,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -432,18 +444,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -781,17 +781,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160D82D4-F57D-4CFD-BFA4-F37D7E897A75}">
   <dimension ref="C1:H30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="31.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C2" s="14" t="s">
         <v>18</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="G2" s="16"/>
       <c r="H2" s="24"/>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" s="17" t="s">
         <v>19</v>
       </c>
@@ -811,7 +811,7 @@
       <c r="G3" s="18"/>
       <c r="H3" s="24"/>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="17" t="s">
         <v>20</v>
       </c>
@@ -821,7 +821,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="24"/>
     </row>
-    <row r="5" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="19" t="s">
         <v>23</v>
       </c>
@@ -831,7 +831,7 @@
       <c r="G5" s="21"/>
       <c r="H5" s="24"/>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" s="23"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -839,21 +839,21 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="31" t="s">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="34"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="8" t="s">
         <v>5</v>
       </c>
@@ -861,14 +861,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="26"/>
+      <c r="D9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="30"/>
       <c r="F9" s="3">
         <v>0.5</v>
       </c>
@@ -877,14 +877,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="26"/>
+      <c r="D10" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="30"/>
       <c r="F10" s="3">
         <v>0.5</v>
       </c>
@@ -893,14 +893,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="26"/>
+      <c r="D11" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="30"/>
       <c r="F11" s="3">
         <v>0.5</v>
       </c>
@@ -909,14 +909,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="26"/>
+      <c r="D12" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="30"/>
       <c r="F12" s="3">
         <v>0.5</v>
       </c>
@@ -925,7 +925,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
         <v>26</v>
       </c>
@@ -939,7 +939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="27" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="10" t="s">
         <v>32</v>
@@ -954,7 +954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C15" s="6" t="s">
         <v>28</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="7" t="s">
         <v>6</v>
       </c>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C17" s="7" t="s">
         <v>7</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C18" s="7" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C19" s="7" t="s">
         <v>9</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C20" s="22" t="s">
         <v>27</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="27" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="D21" s="10" t="s">
         <v>32</v>
@@ -1073,27 +1073,31 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F22" s="3">
         <v>0.5</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" ref="G22:G28" si="2">COUNTIF(D22:E22,"=X")*F22</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E23" s="3" t="s">
         <v>2</v>
       </c>
@@ -1102,14 +1106,16 @@
       </c>
       <c r="G23" s="3">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E24" s="3" t="s">
         <v>2</v>
       </c>
@@ -1118,10 +1124,10 @@
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C25" s="7" t="s">
         <v>16</v>
       </c>
@@ -1137,14 +1143,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="30"/>
+      <c r="D26" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="34"/>
       <c r="F26" s="3">
         <v>0.5</v>
       </c>
@@ -1153,14 +1159,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="30"/>
+      <c r="D27" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="34"/>
       <c r="F27" s="3">
         <v>0.5</v>
       </c>
@@ -1169,23 +1175,21 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C28" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="26"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="30"/>
       <c r="F28" s="3">
         <v>0.5</v>
       </c>
       <c r="G28" s="3">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C29" s="22" t="s">
         <v>26</v>
       </c>
@@ -1199,13 +1203,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="27" t="s">
+    <row r="30" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C30" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="8">
         <f>MIN(10,SUM(G29,G20,G13))</f>
         <v>10</v>
@@ -1213,16 +1217,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/T2 - Práctica React - 29012026/T2 - Tabla puntuación.xlsx
+++ b/T2 - Práctica React - 29012026/T2 - Tabla puntuación.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Equipo\Desktop\Oficina-DAM\2ºDAM\DIDAHE\T2 - Práctica React - 29012026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3646E4-7083-4ADC-B52B-44451E6760A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4936A5D4-1B23-4F21-A692-807F4578CDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{360ED738-5174-48CE-9540-6C3D0194F059}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
   <si>
     <t>APLICACIÓN</t>
   </si>
@@ -139,7 +139,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +188,13 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -362,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -416,18 +423,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -444,6 +439,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -840,20 +853,20 @@
       <c r="H6" s="24"/>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="8" t="s">
         <v>5</v>
       </c>
@@ -865,10 +878,10 @@
       <c r="C9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="30"/>
+      <c r="D9" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="26"/>
       <c r="F9" s="3">
         <v>0.5</v>
       </c>
@@ -881,10 +894,10 @@
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="30"/>
+      <c r="D10" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="26"/>
       <c r="F10" s="3">
         <v>0.5</v>
       </c>
@@ -897,10 +910,10 @@
       <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="30"/>
+      <c r="D11" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="26"/>
       <c r="F11" s="3">
         <v>0.5</v>
       </c>
@@ -913,10 +926,10 @@
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="30"/>
+      <c r="D12" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="26"/>
       <c r="F12" s="3">
         <v>0.5</v>
       </c>
@@ -1134,23 +1147,25 @@
       <c r="D25" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F25" s="3">
         <v>0.5</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="34"/>
+      <c r="D26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="30"/>
       <c r="F26" s="3">
         <v>0.5</v>
       </c>
@@ -1163,10 +1178,10 @@
       <c r="C27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="34"/>
+      <c r="D27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="30"/>
       <c r="F27" s="3">
         <v>0.5</v>
       </c>
@@ -1179,8 +1194,8 @@
       <c r="C28" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="30"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="3">
         <v>0.5</v>
       </c>
@@ -1204,12 +1219,12 @@
       </c>
     </row>
     <row r="30" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29"/>
       <c r="G30" s="8">
         <f>MIN(10,SUM(G29,G20,G13))</f>
         <v>10</v>
@@ -1217,16 +1232,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
